--- a/docs/workbook-split/dateien/Rückstellungen.xlsx
+++ b/docs/workbook-split/dateien/Rückstellungen.xlsx
@@ -637,16 +637,14 @@
       <c r="G7" s="6" t="n">
         <v>57000</v>
       </c>
-      <c r="H7" s="6">
-        <f>E7-F7+G7</f>
-        <v/>
+      <c r="H7" s="6" t="n">
+        <v>57000</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>57000</v>
       </c>
-      <c r="J7" s="6">
-        <f>H7-I7</f>
-        <v/>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n"/>
       <c r="L7" s="1" t="n"/>
@@ -673,16 +671,14 @@
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6">
-        <f>E8-F8+G8</f>
-        <v/>
+      <c r="H8" s="6" t="n">
+        <v>250.8</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>250.8</v>
       </c>
-      <c r="J8" s="6">
-        <f>H8-I8</f>
-        <v/>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
@@ -709,16 +705,14 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6">
-        <f>E9-F9+G9</f>
-        <v/>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="6">
-        <f>H9-I9</f>
-        <v/>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
@@ -745,16 +739,14 @@
       <c r="G10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6">
-        <f>E10-F10+G10</f>
-        <v/>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="6">
-        <f>H10-I10</f>
-        <v/>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
@@ -781,16 +773,14 @@
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6">
-        <f>E11-F11+G11</f>
-        <v/>
+      <c r="H11" s="6" t="n">
+        <v>11182</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>11182</v>
       </c>
-      <c r="J11" s="6">
-        <f>H11-I11</f>
-        <v/>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
@@ -817,16 +807,14 @@
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6">
-        <f>E12-F12+G12</f>
-        <v/>
+      <c r="H12" s="6" t="n">
+        <v>287.8000000000029</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>287.8</v>
       </c>
-      <c r="J12" s="6">
-        <f>H12-I12</f>
-        <v/>
+      <c r="J12" s="6" t="n">
+        <v>2.899014361901209e-12</v>
       </c>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
@@ -853,16 +841,14 @@
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="6">
-        <f>E13-F13+G13</f>
-        <v/>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="6">
-        <f>H13-I13</f>
-        <v/>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
@@ -889,16 +875,14 @@
       <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6">
-        <f>E14-F14+G14</f>
-        <v/>
+      <c r="H14" s="6" t="n">
+        <v>108635.41</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>108635.41</v>
       </c>
-      <c r="J14" s="6">
-        <f>H14-I14</f>
-        <v/>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
@@ -925,16 +909,14 @@
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6">
-        <f>E15-F15+G15</f>
-        <v/>
+      <c r="H15" s="6" t="n">
+        <v>66505.64999999999</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>66505.64999999999</v>
       </c>
-      <c r="J15" s="6">
-        <f>H15-I15</f>
-        <v/>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="n"/>
       <c r="L15" s="1" t="n"/>
@@ -961,16 +943,14 @@
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6">
-        <f>E16-F16+G16</f>
-        <v/>
+      <c r="H16" s="6" t="n">
+        <v>75406.8</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>75406.8</v>
       </c>
-      <c r="J16" s="6">
-        <f>H16-I16</f>
-        <v/>
+      <c r="J16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
@@ -997,16 +977,14 @@
       <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="6">
-        <f>E17-F17+G17</f>
-        <v/>
+      <c r="H17" s="6" t="n">
+        <v>29.56</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>29.56</v>
       </c>
-      <c r="J17" s="6">
-        <f>H17-I17</f>
-        <v/>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n"/>
       <c r="L17" s="1" t="n"/>
@@ -1033,16 +1011,14 @@
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6">
-        <f>E18-F18+G18</f>
-        <v/>
+      <c r="H18" s="6" t="n">
+        <v>509383</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>509383</v>
       </c>
-      <c r="J18" s="6">
-        <f>H18-I18</f>
-        <v/>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="n"/>
       <c r="L18" s="1" t="n"/>
@@ -1635,6 +1611,8 @@
       <c r="K60" s="1" t="n"/>
       <c r="L60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
